--- a/vibe_code_apps_20/wattlab/notebooks/templates/ecm_package_v1.xlsx
+++ b/vibe_code_apps_20/wattlab/notebooks/templates/ecm_package_v1.xlsx
@@ -4,17 +4,20 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inputs" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ESCO_Calcs" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPlus_Results" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Compare" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ROI_Capital" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guardrails" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Docs" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Screening_Results" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calibrated_Twin" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inputs" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ESCO_Calcs" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPlus_Results" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Compare" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ROI_Capital" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guardrails" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Docs" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Charts" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="inp_area_ft2">'Inputs'!$B$2</definedName>
@@ -27,6 +30,19 @@
     <definedName name="inp_life_years">'Inputs'!$B$9</definedName>
     <definedName name="inp_usd_per_ft2">'Inputs'!$B$10</definedName>
     <definedName name="inp_coverage">'Inputs'!$B$11</definedName>
+    <definedName name="inp_sched_hours_saved">'Inputs'!$B$12</definedName>
+    <definedName name="inp_fan_hours">'Inputs'!$B$13</definedName>
+    <definedName name="inp_fan_speed">'Inputs'!$B$14</definedName>
+    <definedName name="inp_kw_per_ton">'Inputs'!$B$15</definedName>
+    <definedName name="inp_lockout_hours">'Inputs'!$B$16</definedName>
+    <definedName name="inp_standby_hours">'Inputs'!$B$17</definedName>
+    <definedName name="inp_sat_hours">'Inputs'!$B$18</definedName>
+    <definedName name="inp_erv_cfm">'Inputs'!$B$19</definedName>
+    <definedName name="inp_erv_eff">'Inputs'!$B$20</definedName>
+    <definedName name="inp_erv_hours">'Inputs'!$B$21</definedName>
+    <definedName name="inp_heating_mmbtu">'Inputs'!$B$22</definedName>
+    <definedName name="inp_boiler_eff_base">'Inputs'!$B$23</definedName>
+    <definedName name="inp_boiler_eff_prop">'Inputs'!$B$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -35,7 +51,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -57,6 +73,10 @@
     <font>
       <b val="1"/>
       <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="13"/>
     </font>
   </fonts>
   <fills count="4">
@@ -89,13 +109,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -170,6 +191,251 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Electric savings — ESCO screening (kWh/yr)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Charts'!B4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Charts'!$G$5:$G$11</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Charts'!$B$5:$B$11</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>kWh/yr</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="11"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Annual utility $ saved — screening</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Charts'!E4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Charts'!$G$5:$G$11</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Charts'!$E$5:$E$11</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>$/yr</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7200000" cy="3960000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>21</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7200000" cy="3960000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -461,7 +727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -478,10 +744,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ECM package screening (ESCO bin-method vs EnergyPlus)</t>
-        </is>
-      </c>
-    </row>
+          <t>ECM package screening (agent-owned Excel · Studio = mirror)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -514,94 +781,639 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1 · Controls-first (no capital RCx)</t>
+          <t>Easy RCx — schedules, sensors, standby+DCV, chiller lockout (no major capital)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Honesty</t>
+          <t>Catalog label</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>screening — schedules / sensors / standby+DCV</t>
+          <t>1 · Easy controls (minimal modification)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Generated (UTC)</t>
+          <t>Honesty</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-25T19:56:47Z</t>
+          <t>screening — lowest-touch package before G36 airside</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Catalog package</t>
+          <t>Generated (UTC)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no-capital-rcx</t>
+          <t>2026-07-27T13:45:09Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>n_measures</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>7</v>
+          <t>Catalog package</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>no-capital-rcx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Guardrail verdict</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>INVESTIGATE</t>
-        </is>
+          <t>n_measures</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ESCO docs</t>
+          <t>Twin run</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://github.com/bbartling/py-bacnet-stacks-playground/blob/develop/vibe_code_apps_20/docs/ESCO_SPREADSHEET_CALCS.md</t>
+          <t>(none — E+ optional)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>G14 pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Model site EUI</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Model kWh/yr</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Model therms/yr</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Peer band</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Peer vs median %</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Screening $/sf</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>3.0 (controls-first screening band) — screening ≠ bid / ≠ calibrated ROI</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Guardrail verdict</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>PUBLISH</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ESCO calculators</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>https://github.com/bbartling/py-bacnet-stacks-playground/blob/develop/vibe_code_apps_20/vibe20_agent_spec/docs/ESCO_CALCULATORS.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Retrofit cost / ROI</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>https://github.com/bbartling/py-bacnet-stacks-playground/blob/develop/vibe_code_apps_20/vibe20_agent_spec/docs/ESCO_RETROFIT_COST_ROI.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Spreadsheet map</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>https://github.com/bbartling/py-bacnet-stacks-playground/blob/develop/vibe_code_apps_20/docs/ESCO_SPREADSHEET_CALCS.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Template</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>loaded ecm_package_v1.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Yellow cells on Inputs are engineer-editable. ESCO_Calcs / Compare / ROI use formulas where marked.</t>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Yellow Inputs drive rate-linked Excel formulas (annual $, payback, NPV, cost B=H). Formula-backed ESCO kWh: ECM-AHU-SCHED-ALIGN, ECM-OCC-STANDBY-DCV, ECM-CHILLER-LOCKOUT. Other ESCO rows are Python screening proxies. Screening — not investment-grade. See Docs · ESCO_CALCULATORS · ESCO_RETROFIT_COST_ROI. EPlus_Results empty — measure savings optional; Calibrated_Twin is baseline.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Documentation &amp; calculator map</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ESCO calculators (agent-spec)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>https://github.com/bbartling/py-bacnet-stacks-playground/blob/develop/vibe_code_apps_20/vibe20_agent_spec/docs/ESCO_CALCULATORS.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Retrofit cost / ROI screening</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>https://github.com/bbartling/py-bacnet-stacks-playground/blob/develop/vibe_code_apps_20/vibe20_agent_spec/docs/ESCO_RETROFIT_COST_ROI.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Spreadsheet formula map</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>https://github.com/bbartling/py-bacnet-stacks-playground/blob/develop/vibe_code_apps_20/docs/ESCO_SPREADSHEET_CALCS.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Python bin calculators</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>wattlab/bench/esco.py · skill wattlab-esco-bins</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Crosscheck / finance</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>crosscheck.py · ROI G=Excel NPV; I=Python cache; screening $/sf ≈ 3.0 (controls-first screening band) — not calibrated ROI</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Catalog package</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>no-capital-rcx</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Measure ids</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ECM-AHU-SCHED-ALIGN, ECM-OA-DAMPER-REPAIR, ECM-SENSOR-CRITICAL-REFRESH, ECM-OCC-STANDBY-DCV, ECM-CHILLER-LOCKOUT, ECM-SENSOR-CALIBRATION, ECM-RCX-SETPOINT-REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Calibrated Twin</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Sheet Calibrated_Twin = G14 baseline (not measure savings)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Template file</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>templates/ecm_package_v1.xlsx LOADED then rebuilt (agent-owned Excel; Studio mirrors disk)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Agent CLI</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>wattlab notebook agent-build --package controls_first --twin-run … --out reports/notebooks/ | prefill | refresh-caches | sync-from-twin</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ESCO kWh/therms honesty</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Formula-backed: ECM-AHU-SCHED-ALIGN, ECM-BOILER-RESET, ECM-CHILLER-LOCKOUT, ECM-DSP-RESET, ECM-ERV, ECM-OCC-STANDBY-DCV, ECM-PREMIUM-FAN-VFD, ECM-SAT-RESET. Others: Python proxy at build. Screening — not investment-grade.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Measure charts (formula-linked — trace to Compare · ESCO_Calcs · Screening_Results)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Chart_Data rows reference live workbook formulas. When Twin cascade is missing, twin_kwh and % diff stay blank; screening charts still plot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>measure_id</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>screening_kwh</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>twin_kwh</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>pct_diff_twin_vs_screening</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>annual_usd</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>payback_yr</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>chart_label</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ECM-AHU-SCHED-ALIGN</t>
+        </is>
+      </c>
+      <c r="B5">
+        <f>ESCO_Calcs!B2</f>
+        <v/>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5">
+        <f>Screening_Results!F2</f>
+        <v/>
+      </c>
+      <c r="F5">
+        <f>Screening_Results!H2</f>
+        <v/>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ALIGN</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ECM-OA-DAMPER-REPAIR</t>
+        </is>
+      </c>
+      <c r="B6">
+        <f>ESCO_Calcs!B3</f>
+        <v/>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6">
+        <f>Screening_Results!F3</f>
+        <v/>
+      </c>
+      <c r="F6">
+        <f>Screening_Results!H3</f>
+        <v/>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>REPAIR</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ECM-SENSOR-CRITICAL-REFRESH</t>
+        </is>
+      </c>
+      <c r="B7">
+        <f>ESCO_Calcs!B4</f>
+        <v/>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7">
+        <f>Screening_Results!F4</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f>Screening_Results!H4</f>
+        <v/>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>REFRESH</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ECM-OCC-STANDBY-DCV</t>
+        </is>
+      </c>
+      <c r="B8">
+        <f>ESCO_Calcs!B5</f>
+        <v/>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8">
+        <f>Screening_Results!F5</f>
+        <v/>
+      </c>
+      <c r="F8">
+        <f>Screening_Results!H5</f>
+        <v/>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>DCV</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ECM-CHILLER-LOCKOUT</t>
+        </is>
+      </c>
+      <c r="B9">
+        <f>ESCO_Calcs!B6</f>
+        <v/>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9">
+        <f>Screening_Results!F6</f>
+        <v/>
+      </c>
+      <c r="F9">
+        <f>Screening_Results!H6</f>
+        <v/>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>LOCKOUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ECM-SENSOR-CALIBRATION</t>
+        </is>
+      </c>
+      <c r="B10">
+        <f>ESCO_Calcs!B7</f>
+        <v/>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10">
+        <f>Screening_Results!F7</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f>Screening_Results!H7</f>
+        <v/>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>CALIBRATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ECM-RCX-SETPOINT-REVIEW</t>
+        </is>
+      </c>
+      <c r="B11">
+        <f>ESCO_Calcs!B8</f>
+        <v/>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11">
+        <f>Screening_Results!F8</f>
+        <v/>
+      </c>
+      <c r="F11">
+        <f>Screening_Results!H8</f>
+        <v/>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Twin charts pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>No measure-level EnergyPlus cascade — attach savings_by_measure to populate twin_kwh and % diff columns, then refresh Charts.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:G2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -611,7 +1423,583 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:J9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="64" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>measure_id</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>basis</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>elec_delta_kwh</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>savings_kwh</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>savings_therms</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>annual_cost_saved_usd</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>implementation_cost_usd</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>simple_payback_years</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>npv_usd</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ECM-AHU-SCHED-ALIGN</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>excel_formula</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F2" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G2" t="n">
+        <v>7500</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="I2" t="n">
+        <v>39515.24</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Build-time screening numbers for Studio. Live Excel formulas are on ESCO_Calcs / ROI_Capital.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ECM-OA-DAMPER-REPAIR</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>python_proxy</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>13000</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="n">
+        <v>-13000</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Build-time screening numbers for Studio. Live Excel formulas are on ESCO_Calcs / ROI_Capital.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ECM-SENSOR-CRITICAL-REFRESH</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>python_proxy</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>17500</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="n">
+        <v>-17500</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Build-time screening numbers for Studio. Live Excel formulas are on ESCO_Calcs / ROI_Capital.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ECM-OCC-STANDBY-DCV</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>excel_formula</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2400</v>
+      </c>
+      <c r="G5" t="n">
+        <v>32500</v>
+      </c>
+      <c r="H5" t="n">
+        <v>13.54</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-4290.85</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Build-time screening numbers for Studio. Live Excel formulas are on ESCO_Calcs / ROI_Capital.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ECM-CHILLER-LOCKOUT</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>excel_formula</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>6000</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="n">
+        <v>-6000</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Build-time screening numbers for Studio. Live Excel formulas are on ESCO_Calcs / ROI_Capital.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ECM-SENSOR-CALIBRATION</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>python_proxy</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>13000</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="n">
+        <v>-13000</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Build-time screening numbers for Studio. Live Excel formulas are on ESCO_Calcs / ROI_Capital.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ECM-RCX-SETPOINT-REVIEW</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>python_proxy</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>277595.8</v>
+      </c>
+      <c r="D8" t="n">
+        <v>277595.8</v>
+      </c>
+      <c r="E8" t="n">
+        <v>5845.4</v>
+      </c>
+      <c r="F8" t="n">
+        <v>37987.82</v>
+      </c>
+      <c r="G8" t="n">
+        <v>13000</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="I8" t="n">
+        <v>433501.59</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Build-time screening numbers for Studio. Live Excel formulas are on ESCO_Calcs / ROI_Capital.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="F9">
+        <f>SUM(F2:F8)</f>
+        <v/>
+      </c>
+      <c r="G9">
+        <f>SUM(G2:G8)</f>
+        <v/>
+      </c>
+      <c r="I9">
+        <f>SUM(I2:I8)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>parameter</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>twin_run</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>(none)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Studio / runs/&lt;id&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>g14_pass</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ASHRAE 14 monthly utility bills</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>model_kwh</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>E+ annual electricity</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>model_therms</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>E+ annual gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>model_site_eui</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>kBtu/ft²-yr</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>bill_kwh</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Observed bills (if joined)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>bill_therms</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Observed bills (if joined)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>nmbe_elec_pct</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Electricity NMBE %</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>cvrmse_elec_pct</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Electricity CV(RMSE) %</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>nmbe_gas_pct</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Gas NMBE %</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>cvrmse_gas_pct</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Gas CV(RMSE) %</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>peer_band</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>vs public EUI peers</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>peer_vs_median_pct</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>+ worse than median</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>scorecard / annual missing — placeholder only; attach --twin-run with calibration_scorecard.json</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>honesty</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Baseline calibrated model — not ECM measure savings (see EPlus_Results).</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>baseline ≠ measure savings</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -837,12 +2225,272 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>sched_hours_saved</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>2500</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>h/yr</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Avoided AHU hours (schedule formula)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>fan_hours</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>h/yr</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Fan annual hours (VFD affinity)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>fan_speed</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0–1</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Proposed VFD speed fraction</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>kw_per_ton</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>kW/ton</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Cooling plant intensity</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>lockout_hours</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>800</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>h/yr</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Chiller lockout / econ hours</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>standby_hours</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>h/yr</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Occupied-standby / DCV hours</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>sat_hours</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>3500</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>h/yr</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>SAT reset eligible hours</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>erv_cfm</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>cfm</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>ERV outdoor / exhaust CFM</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>erv_eff</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0–1</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ERV sensible effectiveness</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>erv_hours</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>h/yr</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>ERV operating hours</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>heating_mmbtu</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>MMBtu/yr</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Annual heating load</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>boiler_eff_base</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>fraction</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Baseline boiler η</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>boiler_eff_prop</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>fraction</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Proposed boiler η (reset/tune)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -895,20 +2543,26 @@
           <t>ECM-AHU-SCHED-ALIGN</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>277595.8</v>
-      </c>
-      <c r="C2" t="n">
-        <v>5845.4</v>
-      </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="B2">
+        <f>IF(OR(inp_fan_hp="",inp_fan_hp=0),0,inp_fan_hp*0.746*inp_sched_hours_saved)+IF(OR(inp_cooling_tons="",inp_cooling_tons=0),0,inp_cooling_tons*inp_kw_per_ton*inp_sched_hours_saved*0.15)</f>
+        <v/>
+      </c>
+      <c r="C2">
+        <f>IF(OR(inp_area_ft2="",inp_area_ft2=0),0,inp_area_ft2*0.0004*inp_sched_hours_saved/10)</f>
+        <v/>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>excel_formula</t>
+        </is>
+      </c>
       <c r="E2">
         <f>B2*inp_elec_rate+C2*inp_gas_rate</f>
         <v/>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Screening proxy from wattlab.studio.proxies / bench ESCO bins</t>
+          <t>Excel formula referencing Inputs named ranges (ESCO_CALCULATORS.md / wattlab-esco-bins). Not a silent Python bake.</t>
         </is>
       </c>
     </row>
@@ -931,7 +2585,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Screening proxy from wattlab.studio.proxies / bench ESCO bins</t>
+          <t>proxy (not Excel yet) — Python screening at build</t>
         </is>
       </c>
     </row>
@@ -954,7 +2608,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Screening proxy from wattlab.studio.proxies / bench ESCO bins</t>
+          <t>proxy (not Excel yet) — Python screening at build</t>
         </is>
       </c>
     </row>
@@ -964,15 +2618,17 @@
           <t>ECM-OCC-STANDBY-DCV</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>46111.2</v>
-      </c>
-      <c r="C5" t="n">
-        <v>5042.8</v>
+      <c r="B5">
+        <f>IF(OR(inp_fan_hp="",inp_fan_hp=0),0,inp_fan_hp*0.746*inp_standby_hours*0.45)+IF(OR(inp_cooling_tons="",inp_cooling_tons=0),0,inp_cooling_tons*inp_kw_per_ton*inp_standby_hours*0.12)</f>
+        <v/>
+      </c>
+      <c r="C5">
+        <f>IF(OR(inp_area_ft2="",inp_area_ft2=0),0,inp_area_ft2*0.0003*inp_standby_hours/10)</f>
+        <v/>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>oad_unoccupied_closed,dcv_bins</t>
+          <t>excel_formula</t>
         </is>
       </c>
       <c r="E5">
@@ -981,7 +2637,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Screening proxy from wattlab.studio.proxies / bench ESCO bins</t>
+          <t>Excel formula referencing Inputs named ranges (ESCO_CALCULATORS.md / wattlab-esco-bins). Not a silent Python bake.</t>
         </is>
       </c>
     </row>
@@ -991,20 +2647,25 @@
           <t>ECM-CHILLER-LOCKOUT</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>34524.9</v>
+      <c r="B6">
+        <f>IF(OR(inp_cooling_tons="",inp_cooling_tons=0),0,inp_cooling_tons*inp_kw_per_ton*inp_lockout_hours)</f>
+        <v/>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>excel_formula</t>
+        </is>
+      </c>
       <c r="E6">
         <f>B6*inp_elec_rate+C6*inp_gas_rate</f>
         <v/>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Screening proxy from wattlab.studio.proxies / bench ESCO bins</t>
+          <t>Excel formula referencing Inputs named ranges (ESCO_CALCULATORS.md / wattlab-esco-bins). Not a silent Python bake.</t>
         </is>
       </c>
     </row>
@@ -1027,7 +2688,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Screening proxy from wattlab.studio.proxies / bench ESCO bins</t>
+          <t>proxy (not Excel yet) — Python screening at build</t>
         </is>
       </c>
     </row>
@@ -1050,487 +2711,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Screening proxy from wattlab.studio.proxies / bench ESCO bins</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>measure_id</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>kwh_saved</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>therms_saved</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>peak_kw_delta</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>source</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ECM-AHU-SCHED-ALIGN</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>E+ not run — ESCO only</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ECM-OA-DAMPER-REPAIR</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>E+ not run — ESCO only</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ECM-SENSOR-CRITICAL-REFRESH</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>E+ not run — ESCO only</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ECM-OCC-STANDBY-DCV</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>E+ not run — ESCO only</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>ECM-CHILLER-LOCKOUT</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>E+ not run — ESCO only</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>ECM-SENSOR-CALIBRATION</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>E+ not run — ESCO only</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>ECM-RCX-SETPOINT-REVIEW</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>E+ not run — ESCO only</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>measure_id</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>esco_kwh</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>ep_kwh</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>delta_kwh</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>ratio_ep_esco</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>esco_therms</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>ep_therms</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>verdict</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>light</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ECM-AHU-SCHED-ALIGN</t>
-        </is>
-      </c>
-      <c r="B2">
-        <f>ESCO_Calcs!B2</f>
-        <v/>
-      </c>
-      <c r="C2">
-        <f>EPlus_Results!B2</f>
-        <v/>
-      </c>
-      <c r="D2">
-        <f>IF(OR(C2="",C2=0),"",C2-B2)</f>
-        <v/>
-      </c>
-      <c r="E2">
-        <f>IF(OR(B2=0,C2=""),"",C2/B2)</f>
-        <v/>
-      </c>
-      <c r="F2">
-        <f>ESCO_Calcs!C2</f>
-        <v/>
-      </c>
-      <c r="G2">
-        <f>EPlus_Results!C2</f>
-        <v/>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>INSUFFICIENT_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>YELLOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ECM-OA-DAMPER-REPAIR</t>
-        </is>
-      </c>
-      <c r="B3">
-        <f>ESCO_Calcs!B3</f>
-        <v/>
-      </c>
-      <c r="C3">
-        <f>EPlus_Results!B3</f>
-        <v/>
-      </c>
-      <c r="D3">
-        <f>IF(OR(C3="",C3=0),"",C3-B3)</f>
-        <v/>
-      </c>
-      <c r="E3">
-        <f>IF(OR(B3=0,C3=""),"",C3/B3)</f>
-        <v/>
-      </c>
-      <c r="F3">
-        <f>ESCO_Calcs!C3</f>
-        <v/>
-      </c>
-      <c r="G3">
-        <f>EPlus_Results!C3</f>
-        <v/>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>INSUFFICIENT_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>YELLOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ECM-SENSOR-CRITICAL-REFRESH</t>
-        </is>
-      </c>
-      <c r="B4">
-        <f>ESCO_Calcs!B4</f>
-        <v/>
-      </c>
-      <c r="C4">
-        <f>EPlus_Results!B4</f>
-        <v/>
-      </c>
-      <c r="D4">
-        <f>IF(OR(C4="",C4=0),"",C4-B4)</f>
-        <v/>
-      </c>
-      <c r="E4">
-        <f>IF(OR(B4=0,C4=""),"",C4/B4)</f>
-        <v/>
-      </c>
-      <c r="F4">
-        <f>ESCO_Calcs!C4</f>
-        <v/>
-      </c>
-      <c r="G4">
-        <f>EPlus_Results!C4</f>
-        <v/>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>INSUFFICIENT_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>YELLOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ECM-OCC-STANDBY-DCV</t>
-        </is>
-      </c>
-      <c r="B5">
-        <f>ESCO_Calcs!B5</f>
-        <v/>
-      </c>
-      <c r="C5">
-        <f>EPlus_Results!B5</f>
-        <v/>
-      </c>
-      <c r="D5">
-        <f>IF(OR(C5="",C5=0),"",C5-B5)</f>
-        <v/>
-      </c>
-      <c r="E5">
-        <f>IF(OR(B5=0,C5=""),"",C5/B5)</f>
-        <v/>
-      </c>
-      <c r="F5">
-        <f>ESCO_Calcs!C5</f>
-        <v/>
-      </c>
-      <c r="G5">
-        <f>EPlus_Results!C5</f>
-        <v/>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>INSUFFICIENT_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>YELLOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>ECM-CHILLER-LOCKOUT</t>
-        </is>
-      </c>
-      <c r="B6">
-        <f>ESCO_Calcs!B6</f>
-        <v/>
-      </c>
-      <c r="C6">
-        <f>EPlus_Results!B6</f>
-        <v/>
-      </c>
-      <c r="D6">
-        <f>IF(OR(C6="",C6=0),"",C6-B6)</f>
-        <v/>
-      </c>
-      <c r="E6">
-        <f>IF(OR(B6=0,C6=""),"",C6/B6)</f>
-        <v/>
-      </c>
-      <c r="F6">
-        <f>ESCO_Calcs!C6</f>
-        <v/>
-      </c>
-      <c r="G6">
-        <f>EPlus_Results!C6</f>
-        <v/>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>INSUFFICIENT_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>YELLOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>ECM-SENSOR-CALIBRATION</t>
-        </is>
-      </c>
-      <c r="B7">
-        <f>ESCO_Calcs!B7</f>
-        <v/>
-      </c>
-      <c r="C7">
-        <f>EPlus_Results!B7</f>
-        <v/>
-      </c>
-      <c r="D7">
-        <f>IF(OR(C7="",C7=0),"",C7-B7)</f>
-        <v/>
-      </c>
-      <c r="E7">
-        <f>IF(OR(B7=0,C7=""),"",C7/B7)</f>
-        <v/>
-      </c>
-      <c r="F7">
-        <f>ESCO_Calcs!C7</f>
-        <v/>
-      </c>
-      <c r="G7">
-        <f>EPlus_Results!C7</f>
-        <v/>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>INSUFFICIENT_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>YELLOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>ECM-RCX-SETPOINT-REVIEW</t>
-        </is>
-      </c>
-      <c r="B8">
-        <f>ESCO_Calcs!B8</f>
-        <v/>
-      </c>
-      <c r="C8">
-        <f>EPlus_Results!B8</f>
-        <v/>
-      </c>
-      <c r="D8">
-        <f>IF(OR(C8="",C8=0),"",C8-B8)</f>
-        <v/>
-      </c>
-      <c r="E8">
-        <f>IF(OR(B8=0,C8=""),"",C8/B8)</f>
-        <v/>
-      </c>
-      <c r="F8">
-        <f>ESCO_Calcs!C8</f>
-        <v/>
-      </c>
-      <c r="G8">
-        <f>EPlus_Results!C8</f>
-        <v/>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>INSUFFICIENT_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>YELLOW</t>
+          <t>proxy (not Excel yet) — Python screening at build</t>
         </is>
       </c>
     </row>
@@ -1545,11 +2726,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1560,274 +2741,35 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>implementation_cost_usd</t>
+          <t>kwh_saved</t>
         </is>
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t>kwh_saved</t>
+          <t>therms_saved</t>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
-          <t>therms_saved</t>
+          <t>peak_kw_delta</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>annual_cost_saved_usd</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>simple_payback_years</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>npv_usd</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>cost_formula</t>
+          <t>source</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ECM-AHU-SCHED-ALIGN</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n">
-        <v>150000</v>
-      </c>
-      <c r="C2" t="n">
-        <v>277595.8</v>
-      </c>
-      <c r="D2" t="n">
-        <v>5845.4</v>
-      </c>
-      <c r="E2">
-        <f>C2*inp_elec_rate+D2*inp_gas_rate</f>
-        <v/>
-      </c>
-      <c r="F2">
-        <f>IF(E2=0,"",B2/E2)</f>
-        <v/>
-      </c>
-      <c r="G2" t="n">
-        <v>296501.59</v>
-      </c>
-      <c r="H2">
-        <f>inp_usd_per_ft2*inp_area_ft2*inp_coverage/7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ECM-OA-DAMPER-REPAIR</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n">
-        <v>150000</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3">
-        <f>C3*inp_elec_rate+D3*inp_gas_rate</f>
-        <v/>
-      </c>
-      <c r="F3">
-        <f>IF(E3=0,"",B3/E3)</f>
-        <v/>
-      </c>
-      <c r="G3" t="n">
-        <v>-150000</v>
-      </c>
-      <c r="H3">
-        <f>inp_usd_per_ft2*inp_area_ft2*inp_coverage/7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ECM-SENSOR-CRITICAL-REFRESH</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>150000</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <f>C4*inp_elec_rate+D4*inp_gas_rate</f>
-        <v/>
-      </c>
-      <c r="F4">
-        <f>IF(E4=0,"",B4/E4)</f>
-        <v/>
-      </c>
-      <c r="G4" t="n">
-        <v>-150000</v>
-      </c>
-      <c r="H4">
-        <f>inp_usd_per_ft2*inp_area_ft2*inp_coverage/7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ECM-OCC-STANDBY-DCV</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>150000</v>
-      </c>
-      <c r="C5" t="n">
-        <v>46111.2</v>
-      </c>
-      <c r="D5" t="n">
-        <v>5042.8</v>
-      </c>
-      <c r="E5">
-        <f>C5*inp_elec_rate+D5*inp_gas_rate</f>
-        <v/>
-      </c>
-      <c r="F5">
-        <f>IF(E5=0,"",B5/E5)</f>
-        <v/>
-      </c>
-      <c r="G5" t="n">
-        <v>-37544.43</v>
-      </c>
-      <c r="H5">
-        <f>inp_usd_per_ft2*inp_area_ft2*inp_coverage/7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>ECM-CHILLER-LOCKOUT</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>150000</v>
-      </c>
-      <c r="C6" t="n">
-        <v>34524.9</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <f>C6*inp_elec_rate+D6*inp_gas_rate</f>
-        <v/>
-      </c>
-      <c r="F6">
-        <f>IF(E6=0,"",B6/E6)</f>
-        <v/>
-      </c>
-      <c r="G6" t="n">
-        <v>-101304.1</v>
-      </c>
-      <c r="H6">
-        <f>inp_usd_per_ft2*inp_area_ft2*inp_coverage/7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>ECM-SENSOR-CALIBRATION</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>150000</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <f>C7*inp_elec_rate+D7*inp_gas_rate</f>
-        <v/>
-      </c>
-      <c r="F7">
-        <f>IF(E7=0,"",B7/E7)</f>
-        <v/>
-      </c>
-      <c r="G7" t="n">
-        <v>-150000</v>
-      </c>
-      <c r="H7">
-        <f>inp_usd_per_ft2*inp_area_ft2*inp_coverage/7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>ECM-RCX-SETPOINT-REVIEW</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>150000</v>
-      </c>
-      <c r="C8" t="n">
-        <v>277595.8</v>
-      </c>
-      <c r="D8" t="n">
-        <v>5845.4</v>
-      </c>
-      <c r="E8">
-        <f>C8*inp_elec_rate+D8*inp_gas_rate</f>
-        <v/>
-      </c>
-      <c r="F8">
-        <f>IF(E8=0,"",B8/E8)</f>
-        <v/>
-      </c>
-      <c r="G8" t="n">
-        <v>296501.59</v>
-      </c>
-      <c r="H8">
-        <f>inp_usd_per_ft2*inp_area_ft2*inp_coverage/7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B9">
-        <f>SUM(B2:B8)</f>
-        <v/>
-      </c>
-      <c r="E9">
-        <f>SUM(E2:E8)</f>
-        <v/>
-      </c>
-      <c r="G9">
-        <f>SUM(G2:G8)</f>
-        <v/>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>No measure-level EnergyPlus savings attached — see Calibrated_Twin for G14 baseline. Blank ≠ zero. Screening numbers are on Screening_Results (ESCO proxies).</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1836,6 +2778,451 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>measure_id</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>esco_kwh</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>ep_kwh</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>delta_kwh</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>ratio_ep_esco</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>esco_therms</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>ep_therms</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>verdict</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>light</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>(package)</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>ESCO_ONLY_NO_EP</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>No measure-level EnergyPlus cascade — Calibrated_Twin is G14 baseline only. Use Screening_Results for ESCO / proxy numbers (not Compare traffic lights).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>measure_id</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>implementation_cost_usd</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>kwh_saved</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>therms_saved</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>annual_cost_saved_usd</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>simple_payback_years</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>npv_usd</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>cost_formula</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>npv_usd_at_build</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ECM-AHU-SCHED-ALIGN</t>
+        </is>
+      </c>
+      <c r="B2" s="3">
+        <f>H2</f>
+        <v/>
+      </c>
+      <c r="C2">
+        <f>ESCO_Calcs!B2</f>
+        <v/>
+      </c>
+      <c r="D2">
+        <f>ESCO_Calcs!C2</f>
+        <v/>
+      </c>
+      <c r="E2">
+        <f>C2*inp_elec_rate+D2*inp_gas_rate</f>
+        <v/>
+      </c>
+      <c r="F2">
+        <f>IF(E2=0,"",B2/E2)</f>
+        <v/>
+      </c>
+      <c r="G2">
+        <f>IF(ABS(inp_discount-inp_escalation)&lt;1E-9,-B2+E2*inp_life_years/(1+inp_discount),-B2+E2*(1-((1+inp_escalation)/(1+inp_discount))^inp_life_years)/(inp_discount-inp_escalation))</f>
+        <v/>
+      </c>
+      <c r="H2" t="n">
+        <v>7500</v>
+      </c>
+      <c r="I2" t="n">
+        <v>39515.24</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ECM-OA-DAMPER-REPAIR</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>H3</f>
+        <v/>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <f>C3*inp_elec_rate+D3*inp_gas_rate</f>
+        <v/>
+      </c>
+      <c r="F3">
+        <f>IF(E3=0,"",B3/E3)</f>
+        <v/>
+      </c>
+      <c r="G3">
+        <f>IF(ABS(inp_discount-inp_escalation)&lt;1E-9,-B3+E3*inp_life_years/(1+inp_discount),-B3+E3*(1-((1+inp_escalation)/(1+inp_discount))^inp_life_years)/(inp_discount-inp_escalation))</f>
+        <v/>
+      </c>
+      <c r="H3" t="n">
+        <v>13000</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-13000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ECM-SENSOR-CRITICAL-REFRESH</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>H4</f>
+        <v/>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <f>C4*inp_elec_rate+D4*inp_gas_rate</f>
+        <v/>
+      </c>
+      <c r="F4">
+        <f>IF(E4=0,"",B4/E4)</f>
+        <v/>
+      </c>
+      <c r="G4">
+        <f>IF(ABS(inp_discount-inp_escalation)&lt;1E-9,-B4+E4*inp_life_years/(1+inp_discount),-B4+E4*(1-((1+inp_escalation)/(1+inp_discount))^inp_life_years)/(inp_discount-inp_escalation))</f>
+        <v/>
+      </c>
+      <c r="H4" t="n">
+        <v>17500</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-17500</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ECM-OCC-STANDBY-DCV</t>
+        </is>
+      </c>
+      <c r="B5" s="3">
+        <f>H5</f>
+        <v/>
+      </c>
+      <c r="C5">
+        <f>ESCO_Calcs!B5</f>
+        <v/>
+      </c>
+      <c r="D5">
+        <f>ESCO_Calcs!C5</f>
+        <v/>
+      </c>
+      <c r="E5">
+        <f>C5*inp_elec_rate+D5*inp_gas_rate</f>
+        <v/>
+      </c>
+      <c r="F5">
+        <f>IF(E5=0,"",B5/E5)</f>
+        <v/>
+      </c>
+      <c r="G5">
+        <f>IF(ABS(inp_discount-inp_escalation)&lt;1E-9,-B5+E5*inp_life_years/(1+inp_discount),-B5+E5*(1-((1+inp_escalation)/(1+inp_discount))^inp_life_years)/(inp_discount-inp_escalation))</f>
+        <v/>
+      </c>
+      <c r="H5" t="n">
+        <v>32500</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-4290.85</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ECM-CHILLER-LOCKOUT</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>H6</f>
+        <v/>
+      </c>
+      <c r="C6">
+        <f>ESCO_Calcs!B6</f>
+        <v/>
+      </c>
+      <c r="D6">
+        <f>ESCO_Calcs!C6</f>
+        <v/>
+      </c>
+      <c r="E6">
+        <f>C6*inp_elec_rate+D6*inp_gas_rate</f>
+        <v/>
+      </c>
+      <c r="F6">
+        <f>IF(E6=0,"",B6/E6)</f>
+        <v/>
+      </c>
+      <c r="G6">
+        <f>IF(ABS(inp_discount-inp_escalation)&lt;1E-9,-B6+E6*inp_life_years/(1+inp_discount),-B6+E6*(1-((1+inp_escalation)/(1+inp_discount))^inp_life_years)/(inp_discount-inp_escalation))</f>
+        <v/>
+      </c>
+      <c r="H6" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-6000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ECM-SENSOR-CALIBRATION</t>
+        </is>
+      </c>
+      <c r="B7" s="3">
+        <f>H7</f>
+        <v/>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <f>C7*inp_elec_rate+D7*inp_gas_rate</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f>IF(E7=0,"",B7/E7)</f>
+        <v/>
+      </c>
+      <c r="G7">
+        <f>IF(ABS(inp_discount-inp_escalation)&lt;1E-9,-B7+E7*inp_life_years/(1+inp_discount),-B7+E7*(1-((1+inp_escalation)/(1+inp_discount))^inp_life_years)/(inp_discount-inp_escalation))</f>
+        <v/>
+      </c>
+      <c r="H7" t="n">
+        <v>13000</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-13000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ECM-RCX-SETPOINT-REVIEW</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>H8</f>
+        <v/>
+      </c>
+      <c r="C8" t="n">
+        <v>277595.8</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5845.4</v>
+      </c>
+      <c r="E8">
+        <f>C8*inp_elec_rate+D8*inp_gas_rate</f>
+        <v/>
+      </c>
+      <c r="F8">
+        <f>IF(E8=0,"",B8/E8)</f>
+        <v/>
+      </c>
+      <c r="G8">
+        <f>IF(ABS(inp_discount-inp_escalation)&lt;1E-9,-B8+E8*inp_life_years/(1+inp_discount),-B8+E8*(1-((1+inp_escalation)/(1+inp_discount))^inp_life_years)/(inp_discount-inp_escalation))</f>
+        <v/>
+      </c>
+      <c r="H8" t="n">
+        <v>13000</v>
+      </c>
+      <c r="I8" t="n">
+        <v>433501.59</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B9">
+        <f>SUM(B2:B8)</f>
+        <v/>
+      </c>
+      <c r="E9">
+        <f>SUM(E2:E8)</f>
+        <v/>
+      </c>
+      <c r="G9">
+        <f>SUM(G2:G8)</f>
+        <v/>
+      </c>
+      <c r="I9">
+        <f>SUM(I2:I8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Honesty</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Package screening ≈ $3.0/sf (controls-first screening band). Controls-first / major / deep bands are screening ≠ bid ≠ calibrated G14 ROI (see ESCO_RETROFIT_COST_ROI.md · gate_capital_plan).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1873,12 +3260,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>INVESTIGATE</t>
+          <t>PUBLISH</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>investigate_count=6</t>
+          <t>investigate_count=0</t>
         </is>
       </c>
     </row>
@@ -1924,12 +3311,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>investigate</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ECM-AHU-SCHED-ALIGN: $3.0/building_ft2 is above the 'rcx_tuning' reference band ($0.05-0.5, 2020$, high confidence).</t>
+          <t>ECM-RCX-SETPOINT-REVIEW: $0.26/building_ft2 vs 'rcx_tuning' band $0.05-0.5 (2020$).</t>
         </is>
       </c>
     </row>
@@ -1941,12 +3328,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>investigate</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ECM-RCX-SETPOINT-REVIEW: $3.0/building_ft2 is above the 'rcx_tuning' reference band ($0.05-0.5, 2020$, high confidence).</t>
+          <t>ECM-AHU-SCHED-ALIGN: $0.15/building_ft2 vs 'rcx_tuning' band $0.05-0.5 (2020$).</t>
         </is>
       </c>
     </row>
@@ -1963,7 +3350,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ECM-OCC-STANDBY-DCV: $3.0/building_ft2 vs 'minor_hvac_controls' band $1.5-3.5 (2017$).</t>
+          <t>ECM-OCC-STANDBY-DCV: $0.65/building_ft2 vs 'minor_hvac_controls' band $1.5-3.5 (2017$).</t>
         </is>
       </c>
     </row>
@@ -1975,12 +3362,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>investigate</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ECM-CHILLER-LOCKOUT: $3.0/building_ft2 is above the 'rcx_tuning' reference band ($0.05-0.5, 2020$, high confidence).</t>
+          <t>ECM-OA-DAMPER-REPAIR: $0.26/building_ft2 vs 'rcx_tuning' band $0.05-0.5 (2020$).</t>
         </is>
       </c>
     </row>
@@ -1992,12 +3379,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>investigate</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ECM-OA-DAMPER-REPAIR: $3.0/building_ft2 is above the 'rcx_tuning' reference band ($0.05-0.5, 2020$, high confidence).</t>
+          <t>ECM-SENSOR-CRITICAL-REFRESH: $0.35/building_ft2 vs 'rcx_tuning' band $0.05-0.5 (2020$).</t>
         </is>
       </c>
     </row>
@@ -2009,12 +3396,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>investigate</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ECM-SENSOR-CRITICAL-REFRESH: $3.0/building_ft2 is above the 'rcx_tuning' reference band ($0.05-0.5, 2020$, high confidence).</t>
+          <t>ECM-CHILLER-LOCKOUT: $0.12/building_ft2 vs 'rcx_tuning' band $0.05-0.5 (2020$).</t>
         </is>
       </c>
     </row>
@@ -2026,121 +3413,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>investigate</t>
+          <t>ok</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ECM-SENSOR-CALIBRATION: $3.0/building_ft2 is above the 'rcx_tuning' reference band ($0.05-0.5, 2020$, high confidence).</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>Documentation &amp; calculator map</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ESCO spreadsheet calcs (human map)</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>https://github.com/bbartling/py-bacnet-stacks-playground/blob/develop/vibe_code_apps_20/docs/ESCO_SPREADSHEET_CALCS.md</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Python bin calculators</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>wattlab/bench/esco.py · wattlab/studio/proxies.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Crosscheck</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>wattlab/crosscheck.py (~0.5–2× = reasonable)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Finance / NPV</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>wattlab/finance.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Catalog package</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>no-capital-rcx</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Measure ids</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>ECM-AHU-SCHED-ALIGN, ECM-OA-DAMPER-REPAIR, ECM-SENSOR-CRITICAL-REFRESH, ECM-OCC-STANDBY-DCV, ECM-CHILLER-LOCKOUT, ECM-SENSOR-CALIBRATION, ECM-RCX-SETPOINT-REVIEW</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Agent CLI</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>wattlab notebook build --package controls_first --out reports/notebooks/</t>
+          <t>ECM-SENSOR-CALIBRATION: $0.26/building_ft2 vs 'rcx_tuning' band $0.05-0.5 (2020$).</t>
         </is>
       </c>
     </row>
